--- a/2026年下半年减肥记录每一天.xlsx
+++ b/2026年下半年减肥记录每一天.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>时间</t>
   </si>
@@ -85,10 +85,47 @@
     <t>中午</t>
   </si>
   <si>
-    <t>三木桔健康餐</t>
+    <t>三木桔蔬菜 + 1/2玉米 + 鸡腿2</t>
+  </si>
+  <si>
+    <t>鸡腿2</t>
+  </si>
+  <si>
+    <t>1/2玉米</t>
+  </si>
+  <si>
+    <t>三木桔蔬菜</t>
   </si>
   <si>
     <t>晚上</t>
+  </si>
+  <si>
+    <t>8个包子</t>
+  </si>
+  <si>
+    <t>不太满意，吃多了</t>
+  </si>
+  <si>
+    <t>2026-8-26 周三</t>
+  </si>
+  <si>
+    <t>2个酸菜包子 + 小西红柿2 + 鸡蛋2</t>
+  </si>
+  <si>
+    <t>鸡蛋2</t>
+  </si>
+  <si>
+    <t>2个酸菜包子</t>
+  </si>
+  <si>
+    <t>小西红柿2</t>
+  </si>
+  <si>
+    <t>满意，生活化</t>
+  </si>
+  <si>
+    <t>目前83.15kg
+本周争取到82kg，加油</t>
   </si>
 </sst>
 </file>
@@ -1124,36 +1161,64 @@
       <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="6"/>
       <c r="B4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="G4" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="6"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="4"/>
+      <c r="A6" s="6"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -1163,7 +1228,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="4"/>
+      <c r="A7" s="6"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>

--- a/2026年下半年减肥记录每一天.xlsx
+++ b/2026年下半年减肥记录每一天.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t>时间</t>
   </si>
@@ -126,6 +126,30 @@
   <si>
     <t>目前83.15kg
 本周争取到82kg，加油</t>
+  </si>
+  <si>
+    <t>2026-9-3 周三</t>
+  </si>
+  <si>
+    <t>西红柿1 + 黄瓜1 + 杂粮馒头1 + 鸡蛋2</t>
+  </si>
+  <si>
+    <t>杂粮馒头1</t>
+  </si>
+  <si>
+    <t>西红柿1 + 黄瓜1</t>
+  </si>
+  <si>
+    <t>盒马 两荤一素</t>
+  </si>
+  <si>
+    <t>鸡肉</t>
+  </si>
+  <si>
+    <t>小碗米饭</t>
+  </si>
+  <si>
+    <t>比较满意，生活化</t>
   </si>
 </sst>
 </file>
@@ -1238,27 +1262,53 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="A8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="4"/>
+      <c r="A10" s="6"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
